--- a/数据表/Fortress.xlsx
+++ b/数据表/Fortress.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>npcid_k</t>
   </si>
@@ -64,7 +64,7 @@
     <t>fee</t>
   </si>
   <si>
-    <t>build_time</t>
+    <t>InitialSoldiers</t>
   </si>
   <si>
     <t>int</t>
@@ -91,7 +91,7 @@
     <t>城的类型</t>
   </si>
   <si>
-    <t>阵营1=玩家，2=敌人1，3=敌人2</t>
+    <t>阵营1=玩家，2=中立城，3=敌人1，3=敌人2</t>
   </si>
   <si>
     <t>等级</t>
@@ -100,7 +100,7 @@
     <t>城模型</t>
   </si>
   <si>
-    <t>基础属性(属性id，值)，(属性id，值)</t>
+    <t>属性id</t>
   </si>
   <si>
     <t>攻击距离</t>
@@ -112,37 +112,28 @@
     <t>兵力上限</t>
   </si>
   <si>
-    <t>士兵建造时间单位秒</t>
+    <t>初始兵种和数量</t>
   </si>
   <si>
     <t>城市1</t>
   </si>
   <si>
-    <t>(Att,2),(Hp,10),(Vision,10)</t>
+    <t>100010001|20</t>
   </si>
   <si>
     <t>城市2</t>
   </si>
   <si>
-    <t>(Att,2),(Hp,11),(Vision,10)</t>
-  </si>
-  <si>
     <t>城市3</t>
   </si>
   <si>
-    <t>(Att,2),(Hp,12),(Vision,10)</t>
-  </si>
-  <si>
     <t>城市4</t>
   </si>
   <si>
-    <t>(Att,2),(Hp,13),(Vision,10)</t>
+    <t>100010001|20;100020001|20</t>
   </si>
   <si>
     <t>城市5</t>
-  </si>
-  <si>
-    <t>(Att,2),(Hp,14),(Vision,10)</t>
   </si>
 </sst>
 </file>
@@ -758,12 +749,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1082,15 +1076,16 @@
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="11.875" customWidth="1"/>
     <col min="3" max="3" width="12.375" customWidth="1"/>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
-    <col min="5" max="5" width="17.25" customWidth="1"/>
+    <col min="4" max="5" width="13.125" customWidth="1"/>
     <col min="6" max="6" width="15.5" customWidth="1"/>
     <col min="7" max="7" width="9.875" customWidth="1"/>
-    <col min="8" max="8" width="18.375" customWidth="1"/>
-    <col min="9" max="9" width="32.375" customWidth="1"/>
-    <col min="10" max="10" width="23.75" customWidth="1"/>
-    <col min="11" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="19" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="16.875" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="11" width="18.875" customWidth="1"/>
+    <col min="12" max="12" width="16.875" customWidth="1"/>
+    <col min="13" max="13" width="26.875" customWidth="1"/>
+    <col min="14" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1154,7 +1149,7 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
         <v>12</v>
@@ -1166,10 +1161,10 @@
         <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:13">
+    <row r="3" customFormat="1" ht="40.5" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -1206,7 +1201,7 @@
       <c r="L3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1229,17 +1224,20 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>1001001</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4">
+        <v>10020001</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4" t="s">
         <v>29</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:13">
@@ -1261,25 +1259,28 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>1001001</v>
       </c>
-      <c r="I5" t="s">
-        <v>31</v>
+      <c r="I5">
+        <v>10020002</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="M5">
-        <v>2</v>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:13">
+    <row r="6" customFormat="1" spans="1:12">
       <c r="A6">
         <v>100010003</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>1000016</v>
@@ -1293,17 +1294,17 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>1001001</v>
       </c>
-      <c r="I6" t="s">
-        <v>33</v>
+      <c r="I6">
+        <v>10020003</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>2</v>
+      <c r="L6">
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:13">
@@ -1311,7 +1312,7 @@
         <v>100010004</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1000016</v>
@@ -1325,17 +1326,20 @@
       <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>1001001</v>
       </c>
-      <c r="I7" t="s">
-        <v>35</v>
+      <c r="I7">
+        <v>10020004</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="M7">
-        <v>2</v>
+      <c r="L7">
+        <v>120</v>
+      </c>
+      <c r="M7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:13">
@@ -1343,7 +1347,7 @@
         <v>100010005</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>1000016</v>
@@ -1357,25 +1361,28 @@
       <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>1001001</v>
       </c>
-      <c r="I8" t="s">
-        <v>37</v>
+      <c r="I8">
+        <v>10020005</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
-      <c r="M8">
-        <v>2</v>
+      <c r="L8">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:13">
+    <row r="9" customFormat="1" spans="1:12">
       <c r="A9">
         <v>100010006</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>1000016</v>
@@ -1389,17 +1396,17 @@
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>1001001</v>
       </c>
-      <c r="I9" t="s">
-        <v>37</v>
+      <c r="I9">
+        <v>10020006</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="M9">
-        <v>2</v>
+      <c r="L9">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
